--- a/i18n/sheet.xlsx
+++ b/i18n/sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22823"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22904"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehealthtrifork-my.sharepoint.com/personal/asg_dawnhealth_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1306" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{60A27A9B-E8F9-4E4C-890C-9200952112AA}"/>
+  <xr:revisionPtr revIDLastSave="1323" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{4CEB9BDA-EA37-4FC5-B0B5-0D790A48F3EB}"/>
   <bookViews>
-    <workbookView xWindow="60840" yWindow="2260" windowWidth="37540" windowHeight="25260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="60840" yWindow="2260" windowWidth="37540" windowHeight="25260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="guidelines (IFU)" sheetId="3" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="643">
   <si>
     <t>English</t>
   </si>
@@ -1620,6 +1620,12 @@
     <t>Guides</t>
   </si>
   <si>
+    <t>menu_transmitters</t>
+  </si>
+  <si>
+    <t>Transmitters</t>
+  </si>
+  <si>
     <t>menu_settings</t>
   </si>
   <si>
@@ -1627,6 +1633,18 @@
   </si>
   <si>
     <t>Indstillinger</t>
+  </si>
+  <si>
+    <t>menu_subitem_profile</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>Profil</t>
+  </si>
+  <si>
+    <t>manu_subitem_profile</t>
   </si>
   <si>
     <t>menu_subItem_about</t>
@@ -1951,9 +1969,6 @@
   </si>
   <si>
     <t>transmitters_title</t>
-  </si>
-  <si>
-    <t>Transmitters</t>
   </si>
   <si>
     <t>transmitters_attached</t>
@@ -4601,7 +4616,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H187"/>
+  <dimension ref="A1:H189"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.42578125" style="2" customWidth="1"/>
@@ -6493,7 +6508,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="15.95">
+    <row r="115" spans="1:8">
       <c r="D115" s="2" t="s">
         <v>492</v>
       </c>
@@ -6504,7 +6519,7 @@
         <v>493</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>492</v>
@@ -6512,39 +6527,39 @@
     </row>
     <row r="116" spans="1:8" ht="15.95">
       <c r="D116" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="E116" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="E116" s="2" t="s">
+      <c r="F116" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="G116" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="F116" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="G116" s="2" t="s">
+      <c r="H116" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="D117" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="H116" s="2" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" ht="15.95">
-      <c r="D117" s="2" t="s">
+      <c r="E117" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="E117" s="2" t="s">
+      <c r="F117" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="G117" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="F117" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="G117" s="2" t="s">
+      <c r="H117" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="H117" s="2" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" ht="15.95">
+    </row>
+    <row r="118" spans="1:8">
       <c r="D118" s="2" t="s">
         <v>501</v>
       </c>
@@ -6595,96 +6610,96 @@
         <v>507</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
-      <c r="A121" s="4"/>
-      <c r="B121" s="4"/>
-      <c r="C121" s="4"/>
-      <c r="D121" s="4"/>
-      <c r="E121" s="4"/>
-      <c r="F121" s="4"/>
-      <c r="G121" s="4"/>
-      <c r="H121" s="4"/>
+    <row r="121" spans="1:8" ht="15.95">
+      <c r="D121" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>510</v>
+      </c>
     </row>
     <row r="122" spans="1:8" ht="15.95">
       <c r="D122" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="F122" s="8" t="s">
-        <v>511</v>
-      </c>
-      <c r="G122" s="8" t="s">
-        <v>512</v>
+        <v>514</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>515</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" ht="15.95">
-      <c r="D123" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="E123" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="F123" s="11" t="s">
-        <v>515</v>
-      </c>
-      <c r="G123" s="11" t="s">
-        <v>515</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>513</v>
-      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" s="4"/>
+      <c r="B123" s="4"/>
+      <c r="C123" s="4"/>
+      <c r="D123" s="4"/>
+      <c r="E123" s="4"/>
+      <c r="F123" s="4"/>
+      <c r="G123" s="4"/>
+      <c r="H123" s="4"/>
     </row>
     <row r="124" spans="1:8" ht="15.95">
       <c r="D124" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="E124" s="8" t="s">
         <v>516</v>
       </c>
+      <c r="E124" s="2" t="s">
+        <v>517</v>
+      </c>
       <c r="F124" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="G124" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="H124" s="2" t="s">
         <v>516</v>
-      </c>
-      <c r="G124" s="8" t="s">
-        <v>517</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="15.95">
       <c r="D125" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="E125" s="8" t="s">
         <v>519</v>
       </c>
-      <c r="F125" s="8" t="s">
+      <c r="E125" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="F125" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="G125" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="H125" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="G125" s="8" t="s">
-        <v>520</v>
-      </c>
-      <c r="H125" s="2" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" ht="32.1">
+    </row>
+    <row r="126" spans="1:8" ht="15.95">
       <c r="D126" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="E126" s="2" t="s">
+      <c r="E126" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="F126" s="11" t="s">
-        <v>515</v>
-      </c>
-      <c r="G126" s="11" t="s">
-        <v>515</v>
+      <c r="F126" s="8" t="s">
+        <v>522</v>
+      </c>
+      <c r="G126" s="8" t="s">
+        <v>523</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>521</v>
@@ -6692,384 +6707,384 @@
     </row>
     <row r="127" spans="1:8" ht="15.95">
       <c r="D127" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E127" s="8" t="s">
-        <v>302</v>
+        <v>525</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>302</v>
+        <v>525</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>303</v>
+        <v>526</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="128" spans="1:8" ht="32.1">
       <c r="D128" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="E128" s="8" t="s">
+        <v>527</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="F128" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="G128" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" ht="15.95">
+      <c r="D129" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="E129" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="F129" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="G129" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="32.1">
+      <c r="D130" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E130" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="F128" s="8" t="s">
+      <c r="F130" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="G128" s="8" t="s">
+      <c r="G130" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="H128" s="2" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" ht="15.95">
-      <c r="A129" s="4" t="s">
-        <v>525</v>
-      </c>
-      <c r="B129" s="4"/>
-      <c r="C129" s="4"/>
-      <c r="D129" s="4"/>
-      <c r="E129" s="4"/>
-      <c r="F129" s="4"/>
-      <c r="G129" s="4"/>
-      <c r="H129" s="4"/>
-    </row>
-    <row r="130" spans="1:8" ht="15.95">
-      <c r="D130" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="F130" s="8" t="s">
-        <v>519</v>
-      </c>
-      <c r="G130" s="8" t="s">
-        <v>520</v>
-      </c>
       <c r="H130" s="2" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
     </row>
     <row r="131" spans="1:8" ht="15.95">
-      <c r="D131" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="F131" s="8" t="s">
-        <v>528</v>
-      </c>
-      <c r="G131" s="8" t="s">
-        <v>529</v>
-      </c>
-      <c r="H131" s="2" t="s">
-        <v>527</v>
-      </c>
+      <c r="A131" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="B131" s="4"/>
+      <c r="C131" s="4"/>
+      <c r="D131" s="4"/>
+      <c r="E131" s="4"/>
+      <c r="F131" s="4"/>
+      <c r="G131" s="4"/>
+      <c r="H131" s="4"/>
     </row>
     <row r="132" spans="1:8" ht="15.95">
       <c r="D132" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8">
-      <c r="A133" s="4"/>
-      <c r="B133" s="4"/>
-      <c r="C133" s="4"/>
-      <c r="D133" s="4"/>
-      <c r="E133" s="4"/>
-      <c r="F133" s="4"/>
-      <c r="G133" s="4"/>
-      <c r="H133" s="4"/>
-    </row>
-    <row r="134" spans="1:8" s="8" customFormat="1" ht="15.95">
-      <c r="D134" s="8" t="s">
-        <v>531</v>
-      </c>
-      <c r="E134" s="8" t="s">
         <v>532</v>
       </c>
+    </row>
+    <row r="133" spans="1:8" ht="15.95">
+      <c r="D133" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="F133" s="8" t="s">
+        <v>534</v>
+      </c>
+      <c r="G133" s="8" t="s">
+        <v>535</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" ht="15.95">
+      <c r="D134" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>522</v>
+      </c>
       <c r="F134" s="8" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>532</v>
-      </c>
-      <c r="H134" s="8" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" s="8" customFormat="1" ht="15.95">
-      <c r="D135" s="8" t="s">
-        <v>533</v>
-      </c>
-      <c r="E135" s="8" t="s">
-        <v>534</v>
-      </c>
-      <c r="F135" s="8" t="s">
-        <v>534</v>
-      </c>
-      <c r="G135" s="8" t="s">
-        <v>534</v>
-      </c>
-      <c r="H135" s="8" t="s">
-        <v>534</v>
-      </c>
+        <v>523</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135" s="4"/>
+      <c r="B135" s="4"/>
+      <c r="C135" s="4"/>
+      <c r="D135" s="4"/>
+      <c r="E135" s="4"/>
+      <c r="F135" s="4"/>
+      <c r="G135" s="4"/>
+      <c r="H135" s="4"/>
     </row>
     <row r="136" spans="1:8" s="8" customFormat="1" ht="15.95">
       <c r="D136" s="8" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E136" s="8" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="F136" s="8" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="H136" s="8" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" ht="15.95">
-      <c r="A137" s="4" t="s">
-        <v>537</v>
-      </c>
-      <c r="B137" s="4"/>
-      <c r="C137" s="4"/>
-      <c r="D137" s="4"/>
-      <c r="E137" s="4"/>
-      <c r="F137" s="4"/>
-      <c r="G137" s="4"/>
-      <c r="H137" s="4"/>
-    </row>
-    <row r="138" spans="1:8" ht="15.95">
-      <c r="D138" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="E138" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="F138" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="G138" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="H138" s="2" t="s">
+    </row>
+    <row r="137" spans="1:8" s="8" customFormat="1" ht="15.95">
+      <c r="D137" s="8" t="s">
         <v>539</v>
       </c>
+      <c r="E137" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="F137" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="G137" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="H137" s="8" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" s="8" customFormat="1" ht="15.95">
+      <c r="D138" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="E138" s="8" t="s">
+        <v>542</v>
+      </c>
+      <c r="F138" s="8" t="s">
+        <v>542</v>
+      </c>
+      <c r="G138" s="8" t="s">
+        <v>542</v>
+      </c>
+      <c r="H138" s="8" t="s">
+        <v>542</v>
+      </c>
     </row>
     <row r="139" spans="1:8" ht="15.95">
-      <c r="D139" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="E139" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="F139" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="G139" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="H139" s="2" t="s">
-        <v>539</v>
-      </c>
+      <c r="A139" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="B139" s="4"/>
+      <c r="C139" s="4"/>
+      <c r="D139" s="4"/>
+      <c r="E139" s="4"/>
+      <c r="F139" s="4"/>
+      <c r="G139" s="4"/>
+      <c r="H139" s="4"/>
     </row>
     <row r="140" spans="1:8" ht="15.95">
       <c r="D140" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>539</v>
+        <v>495</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>539</v>
+        <v>495</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>539</v>
+        <v>496</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
     </row>
     <row r="141" spans="1:8" ht="15.95">
       <c r="D141" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
     </row>
     <row r="142" spans="1:8" ht="15.95">
       <c r="D142" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
     </row>
     <row r="143" spans="1:8" ht="15.95">
       <c r="D143" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="15.95">
       <c r="D144" s="2" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" ht="15.95">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="145" spans="4:8" ht="15.95">
       <c r="D145" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" ht="15.95">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="146" spans="4:8" ht="15.95">
       <c r="D146" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" ht="15.95">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="147" spans="4:8" ht="15.95">
       <c r="D147" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" ht="48">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="148" spans="4:8" ht="15.95">
       <c r="D148" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>560</v>
+        <v>545</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>561</v>
+        <v>545</v>
       </c>
       <c r="G148" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="149" spans="4:8" ht="15.95">
+      <c r="D149" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="H148" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" ht="15.95">
-      <c r="D149" s="2" t="s">
+      <c r="E149" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="E149" s="2" t="s">
+      <c r="F149" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="G149" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="F149" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="G149" s="2" t="s">
+      <c r="H149" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="150" spans="4:8" ht="48">
+      <c r="D150" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="H149" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8" ht="32.1">
-      <c r="D150" s="2" t="s">
+      <c r="E150" s="2" t="s">
         <v>566</v>
-      </c>
-      <c r="E150" s="2" t="s">
-        <v>567</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>567</v>
@@ -7078,10 +7093,10 @@
         <v>568</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8" ht="15.95">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="151" spans="4:8" ht="15.95">
       <c r="D151" s="2" t="s">
         <v>569</v>
       </c>
@@ -7095,587 +7110,621 @@
         <v>571</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" ht="15.95">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="152" spans="4:8" ht="32.1">
       <c r="D152" s="2" t="s">
         <v>572</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>539</v>
+        <v>573</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>539</v>
+        <v>573</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>539</v>
+        <v>574</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" ht="15.95">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="153" spans="4:8" ht="15.95">
       <c r="D153" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" ht="15.95">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="154" spans="4:8" ht="15.95">
       <c r="D154" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" ht="15.95">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="155" spans="4:8" ht="15.95">
       <c r="D155" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>539</v>
+        <v>580</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" ht="48">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="156" spans="4:8" ht="15.95">
       <c r="D156" s="2" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>580</v>
+        <v>545</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>580</v>
+        <v>545</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" ht="15.95">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="157" spans="4:8" ht="15.95">
       <c r="D157" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>582</v>
+        <v>545</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" ht="15.95">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="158" spans="4:8" ht="48">
       <c r="D158" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>584</v>
+        <v>545</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8" ht="15.95">
-      <c r="A159" s="4" t="s">
-        <v>585</v>
-      </c>
-      <c r="B159" s="4"/>
-      <c r="C159" s="4"/>
-      <c r="D159" s="4"/>
-      <c r="E159" s="4"/>
-      <c r="F159" s="4"/>
-      <c r="G159" s="4"/>
-      <c r="H159" s="4"/>
-    </row>
-    <row r="160" spans="1:8" ht="15.95">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="159" spans="4:8" ht="15.95">
+      <c r="D159" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="160" spans="4:8" ht="15.95">
       <c r="D160" s="2" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>539</v>
+        <v>590</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="15.95">
-      <c r="D161" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="E161" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="F161" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="G161" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="H161" s="2" t="s">
-        <v>539</v>
-      </c>
+      <c r="A161" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="B161" s="4"/>
+      <c r="C161" s="4"/>
+      <c r="D161" s="4"/>
+      <c r="E161" s="4"/>
+      <c r="F161" s="4"/>
+      <c r="G161" s="4"/>
+      <c r="H161" s="4"/>
     </row>
     <row r="162" spans="1:8" ht="15.95">
       <c r="D162" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="15.95">
       <c r="D163" s="2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>594</v>
+        <v>545</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>594</v>
+        <v>545</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>595</v>
+        <v>545</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8" ht="20.25" customHeight="1">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" ht="15.95">
       <c r="D164" s="2" t="s">
         <v>596</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>539</v>
+        <v>597</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>539</v>
+        <v>597</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>539</v>
+        <v>598</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
     </row>
     <row r="165" spans="1:8" ht="15.95">
       <c r="D165" s="2" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8" ht="32.1">
-      <c r="A166" s="4" t="s">
-        <v>600</v>
-      </c>
-      <c r="B166" s="4"/>
-      <c r="C166" s="4"/>
-      <c r="D166" s="4"/>
-      <c r="E166" s="4"/>
-      <c r="F166" s="4"/>
-      <c r="G166" s="4"/>
-      <c r="H166" s="4"/>
+        <v>545</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" ht="20.25" customHeight="1">
+      <c r="D166" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="H166" s="2" t="s">
+        <v>545</v>
+      </c>
     </row>
     <row r="167" spans="1:8" ht="15.95">
       <c r="D167" s="2" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>539</v>
+        <v>605</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8" ht="15.95">
-      <c r="D168" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="E168" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="F168" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="G168" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="H168" s="2" t="s">
-        <v>539</v>
-      </c>
+        <v>545</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" ht="32.1">
+      <c r="A168" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="B168" s="4"/>
+      <c r="C168" s="4"/>
+      <c r="D168" s="4"/>
+      <c r="E168" s="4"/>
+      <c r="F168" s="4"/>
+      <c r="G168" s="4"/>
+      <c r="H168" s="4"/>
     </row>
     <row r="169" spans="1:8" ht="15.95">
       <c r="D169" s="2" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>606</v>
+        <v>493</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>606</v>
+        <v>493</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="15.95">
       <c r="D170" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="15.95">
       <c r="D171" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
     </row>
     <row r="172" spans="1:8" ht="15.95">
       <c r="D172" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="15.95">
       <c r="D173" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="15.95">
       <c r="D174" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="15.95">
       <c r="D175" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
     </row>
     <row r="176" spans="1:8" ht="15.95">
       <c r="D176" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>221</v>
+        <v>621</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>221</v>
+        <v>621</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
     </row>
     <row r="177" spans="1:8" ht="15.95">
       <c r="D177" s="2" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="179" spans="1:8" ht="32.1">
-      <c r="A179" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="B179" s="4"/>
-      <c r="C179" s="4"/>
-      <c r="D179" s="4"/>
-      <c r="E179" s="4"/>
-      <c r="F179" s="4"/>
-      <c r="G179" s="4"/>
-      <c r="H179" s="4"/>
-    </row>
-    <row r="180" spans="1:8" ht="15.95">
-      <c r="D180" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="E180" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" ht="15.95">
+      <c r="D178" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="F180" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="G180" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="H180" s="2" t="s">
-        <v>539</v>
+      <c r="E178" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F178" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G178" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="H178" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" ht="15.95">
+      <c r="D179" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="H179" s="2" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="181" spans="1:8" ht="32.1">
-      <c r="D181" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="E181" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="F181" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="G181" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="H181" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="182" spans="1:8" ht="32.1">
+      <c r="A181" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="B181" s="4"/>
+      <c r="C181" s="4"/>
+      <c r="D181" s="4"/>
+      <c r="E181" s="4"/>
+      <c r="F181" s="4"/>
+      <c r="G181" s="4"/>
+      <c r="H181" s="4"/>
+    </row>
+    <row r="182" spans="1:8" ht="15.95">
       <c r="D182" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="32.1">
       <c r="D183" s="2" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="184" spans="1:8" ht="15.95">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" ht="32.1">
       <c r="D184" s="2" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="185" spans="1:8" ht="15.95">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" ht="32.1">
       <c r="D185" s="2" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="186" spans="1:8" ht="32.1">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" ht="15.95">
       <c r="D186" s="2" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="187" spans="1:8" ht="32.1">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" ht="15.95">
       <c r="D187" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>539</v>
+        <v>639</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>539</v>
+        <v>639</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" ht="32.1">
+      <c r="D188" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="H188" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" ht="32.1">
+      <c r="D189" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="H189" s="2" t="s">
+        <v>545</v>
       </c>
     </row>
   </sheetData>
@@ -7685,21 +7734,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001735E4C1AF81B044B42502EF65468AD3" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b06dd55da7e75ffac548536a232936d2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eadb902b-93b7-47a6-8130-18fdf8801a21" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="033944ded8f040f3b5ba86892713db09" ns2:_="">
     <xsd:import namespace="eadb902b-93b7-47a6-8130-18fdf8801a21"/>
@@ -7831,8 +7865,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FBDCD96-85A7-4ED3-BEE8-F34479CB9646}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B7D05CE-367F-41E4-8608-7D898D6C11DA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7840,5 +7889,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B7D05CE-367F-41E4-8608-7D898D6C11DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FBDCD96-85A7-4ED3-BEE8-F34479CB9646}"/>
 </file>
--- a/i18n/sheet.xlsx
+++ b/i18n/sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="23007"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehealthtrifork-my.sharepoint.com/personal/asg_dawnhealth_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1485" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{68905392-9948-45DB-AAD8-E2BB01493553}"/>
+  <xr:revisionPtr revIDLastSave="1541" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{FAD24E1F-7D9B-4D39-8B25-D1497D9AFC07}"/>
   <bookViews>
-    <workbookView xWindow="-49180" yWindow="460" windowWidth="44860" windowHeight="26560" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="38400" windowHeight="21940" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="guidelines (IFU)" sheetId="3" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="D97" authorId="1" shapeId="0" xr:uid="{BDE9ED81-4162-40CF-A238-C26F28E0D936}">
+    <comment ref="D99" authorId="1" shapeId="0" xr:uid="{BDE9ED81-4162-40CF-A238-C26F28E0D936}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -59,7 +59,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="G98" authorId="2" shapeId="0" xr:uid="{42D77C34-74BE-4B4E-A716-C6A2DC88BB9D}">
+    <comment ref="G100" authorId="2" shapeId="0" xr:uid="{42D77C34-74BE-4B4E-A716-C6A2DC88BB9D}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="731">
   <si>
     <t>English</t>
   </si>
@@ -997,6 +997,12 @@
     <t>Confirm</t>
   </si>
   <si>
+    <t>generic_get_started</t>
+  </si>
+  <si>
+    <t>generic_continue</t>
+  </si>
+  <si>
     <t>launch_screen_title</t>
   </si>
   <si>
@@ -1569,6 +1575,12 @@
     <t>lock_notification_moisture</t>
   </si>
   <si>
+    <t>lock_notification_multiple_transmitters</t>
+  </si>
+  <si>
+    <t>[Missing translation]</t>
+  </si>
+  <si>
     <t>lock_notification_total_blind</t>
   </si>
   <si>
@@ -1820,9 +1832,6 @@
   </si>
   <si>
     <t>settings_title</t>
-  </si>
-  <si>
-    <t>[Missing translation]</t>
   </si>
   <si>
     <t>settings_allow_notifications_title</t>
@@ -2103,6 +2112,60 @@
     <t>Choose ringtone</t>
   </si>
   <si>
+    <t>settings_alarm_title</t>
+  </si>
+  <si>
+    <t>settings_alarm_description</t>
+  </si>
+  <si>
+    <t>Set a daily time window for your bedtime leakage alarm to turn on and off.</t>
+  </si>
+  <si>
+    <t>settings_alarm_start</t>
+  </si>
+  <si>
+    <t>settings_alarm_end</t>
+  </si>
+  <si>
+    <t>End</t>
+  </si>
+  <si>
+    <t>settings_alarm_choose_sensors</t>
+  </si>
+  <si>
+    <t>Choose bedtime sensors</t>
+  </si>
+  <si>
+    <t>settings_alarm_message</t>
+  </si>
+  <si>
+    <t>Between the hours of %1$s and %2$s you will receive a continuous alarm if leakage is detected between the ion either inner or outer sensor during the scheduled time or if connection is lost. This will bypass Silent or Do Not Disturb settings.</t>
+  </si>
+  <si>
+    <t>settings_alarm_choose_start</t>
+  </si>
+  <si>
+    <t>Choose start time</t>
+  </si>
+  <si>
+    <t>settings_alarm_choose_end</t>
+  </si>
+  <si>
+    <t>Choose end time</t>
+  </si>
+  <si>
+    <t>settings_sound_alerts_off</t>
+  </si>
+  <si>
+    <t>Sound alerts off</t>
+  </si>
+  <si>
+    <t>settings_sound_alerts_off_warning</t>
+  </si>
+  <si>
+    <t>You currently have no sound alerts on. You might want to turn on sound alerts to avoid missing important notifications.</t>
+  </si>
+  <si>
     <t>dialog settings</t>
   </si>
   <si>
@@ -2260,6 +2323,21 @@
   </si>
   <si>
     <t>dialog_transmitters_delete_title</t>
+  </si>
+  <si>
+    <t>Onboarding</t>
+  </si>
+  <si>
+    <t>onboarding_chapter_intro_setup_guide</t>
+  </si>
+  <si>
+    <t>Setup guide</t>
+  </si>
+  <si>
+    <t>onboarding_chapter_intro_setup_guide_message</t>
+  </si>
+  <si>
+    <t>This guide will guide you step-by-step through the process of setting up TestProduct and applying in to your body.</t>
   </si>
 </sst>
 </file>
@@ -2531,6 +2609,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFD0CECE"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2850,16 +2933,16 @@
     <text xml:space="preserve">should not be "dart. changing back to generic_error
 </text>
   </threadedComment>
-  <threadedComment ref="D97" dT="2020-01-30T11:02:45.05" personId="{B79F2389-A58C-4580-AB7E-F38941B162BC}" id="{BDE9ED81-4162-40CF-A238-C26F28E0D936}">
+  <threadedComment ref="D99" dT="2020-01-30T11:02:45.05" personId="{B79F2389-A58C-4580-AB7E-F38941B162BC}" id="{BDE9ED81-4162-40CF-A238-C26F28E0D936}">
     <text xml:space="preserve">Sam! we need a notifcation text for when the battery is empty. 
 screen: R “no battery”
 </text>
   </threadedComment>
-  <threadedComment ref="D97" dT="2020-01-31T08:03:31.02" personId="{22A1C8B1-5B6A-4FE9-A792-3A8FE3B25A61}" id="{13CB1CE2-D2F5-40C1-8D4E-C698FEB9DD41}" parentId="{BDE9ED81-4162-40CF-A238-C26F28E0D936}">
+  <threadedComment ref="D99" dT="2020-01-31T08:03:31.02" personId="{22A1C8B1-5B6A-4FE9-A792-3A8FE3B25A61}" id="{13CB1CE2-D2F5-40C1-8D4E-C698FEB9DD41}" parentId="{BDE9ED81-4162-40CF-A238-C26F28E0D936}">
     <text xml:space="preserve">Should be ready for you now – let me know if that doesn't work for any reason. Danish by Anne
 </text>
   </threadedComment>
-  <threadedComment ref="G98" dT="2020-01-31T08:02:57.65" personId="{22A1C8B1-5B6A-4FE9-A792-3A8FE3B25A61}" id="{42D77C34-74BE-4B4E-A716-C6A2DC88BB9D}">
+  <threadedComment ref="G100" dT="2020-01-31T08:02:57.65" personId="{22A1C8B1-5B6A-4FE9-A792-3A8FE3B25A61}" id="{42D77C34-74BE-4B4E-A716-C6A2DC88BB9D}">
     <text xml:space="preserve">Updated by Anne
 </text>
   </threadedComment>
@@ -4923,7 +5006,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:XFD226"/>
+  <dimension ref="A1:XFD242"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.42578125" style="2" customWidth="1"/>
@@ -5372,752 +5455,740 @@
       <c r="G27" s="14"/>
       <c r="H27" s="14"/>
     </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-    </row>
-    <row r="29" spans="1:8" ht="15.95">
-      <c r="D29" s="2" t="s">
+    <row r="28" spans="1:8" s="8" customFormat="1" ht="15.75" customHeight="1">
+      <c r="D28" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E28" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+    </row>
+    <row r="29" spans="1:8" s="8" customFormat="1" ht="15.75" customHeight="1">
+      <c r="D29" s="14" t="s">
         <v>286</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="15.95">
-      <c r="D30" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>287</v>
-      </c>
+      <c r="E29" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
     </row>
     <row r="31" spans="1:8" ht="15.95">
       <c r="D31" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="15.95">
       <c r="D32" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="33" spans="4:8" ht="15.95">
       <c r="D33" s="2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34" spans="4:8" ht="15.95">
       <c r="D34" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="35" spans="4:8" ht="15.95">
+      <c r="D35" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="F35" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="F34" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="35" spans="4:8" ht="32.1">
-      <c r="D35" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>304</v>
-      </c>
       <c r="H35" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="4:8" ht="15.95">
       <c r="D36" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="4:8" ht="32.1">
       <c r="D37" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" spans="4:8" ht="15.95">
       <c r="D38" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="39" spans="4:8" ht="32.1">
+      <c r="D39" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="F39" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="G39" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="F38" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="39" spans="4:8" ht="15.95">
-      <c r="D39" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>316</v>
-      </c>
       <c r="H39" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="40" spans="4:8" ht="15.95">
       <c r="D40" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="41" spans="4:8" ht="15.95">
       <c r="D41" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="42" spans="4:8" ht="15.95">
       <c r="D42" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="43" spans="4:8" ht="15.95">
       <c r="D43" s="2" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
     </row>
     <row r="44" spans="4:8" ht="15.95">
       <c r="D44" s="2" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
     </row>
     <row r="45" spans="4:8" ht="15.95">
       <c r="D45" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="46" spans="4:8" ht="15.95">
+      <c r="D46" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="F46" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="F45" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="46" spans="4:8" ht="70.5" customHeight="1">
-      <c r="D46" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>341</v>
-      </c>
       <c r="H46" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
     </row>
     <row r="47" spans="4:8" ht="15.95">
       <c r="D47" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="48" spans="4:8" ht="70.5" customHeight="1">
+      <c r="D48" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="F48" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="G48" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="F47" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="48" spans="4:8" ht="15.95">
-      <c r="D48" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>347</v>
-      </c>
       <c r="H48" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="49" spans="4:8" ht="15.95">
       <c r="D49" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="50" spans="4:8" ht="15.95">
+      <c r="D50" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="F50" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="G50" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="F49" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="50" spans="4:8" ht="32.1">
-      <c r="D50" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>353</v>
-      </c>
       <c r="H50" s="2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="51" spans="4:8" ht="15.95">
       <c r="D51" s="2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="52" spans="4:8" ht="32.1">
       <c r="D52" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="53" spans="4:8" ht="15.95">
       <c r="D53" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="54" spans="4:8" ht="32.1">
+      <c r="D54" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="F54" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="G54" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="F53" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="G53" s="2" t="s">
+      <c r="H54" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="55" spans="4:8" ht="15.95">
+      <c r="D55" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="H53" s="2" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="54" spans="4:8" ht="15.95">
-      <c r="D54" s="2" t="s">
+      <c r="E55" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="F55" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="G55" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="F54" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="55" spans="4:8" ht="32.1">
-      <c r="D55" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>359</v>
-      </c>
       <c r="H55" s="2" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="56" spans="4:8" ht="15.95">
       <c r="D56" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G56" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="H56" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="57" spans="4:8" ht="32.1">
+      <c r="D57" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="F56" s="2" t="s">
+      <c r="E57" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H57" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="G56" s="2" t="s">
+    </row>
+    <row r="58" spans="4:8" ht="15.95">
+      <c r="D58" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="H56" s="2" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="57" spans="4:8" ht="15.95">
-      <c r="D57" s="2" t="s">
+      <c r="E58" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="F58" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="G58" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="F57" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="58" spans="4:8" ht="32.1">
-      <c r="D58" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>375</v>
-      </c>
       <c r="H58" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="59" spans="4:8" ht="15.95">
       <c r="D59" s="2" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="60" spans="4:8" ht="32.1">
       <c r="D60" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="61" spans="4:8" ht="15.95">
       <c r="D61" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="62" spans="4:8" ht="32.1">
       <c r="D62" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="63" spans="4:8" ht="15.95">
+      <c r="D63" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="E62" s="2" t="s">
+      <c r="E63" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="G63" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="F62" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="G62" s="2" t="s">
+      <c r="H63" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="64" spans="4:8" ht="32.1">
+      <c r="D64" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="H62" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="63" spans="4:8" ht="32.1">
-      <c r="D63" s="2" t="s">
+      <c r="E64" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="F64" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="G64" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="F63" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="G63" s="2" t="s">
+      <c r="H64" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="32.1">
+      <c r="D65" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="H63" s="2" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="64" spans="4:8" ht="15.95">
-      <c r="D64" s="2" t="s">
+      <c r="E65" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="E64" s="2" t="s">
+      <c r="F65" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="G65" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="F64" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="G64" s="2" t="s">
+      <c r="H65" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="15.95">
+      <c r="D66" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="H64" s="2" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="15.95">
-      <c r="D65" s="2" t="s">
+      <c r="E66" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="E65" s="2" t="s">
+      <c r="F66" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="G66" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="F65" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="G65" s="2" t="s">
+      <c r="H66" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="15.95">
+      <c r="D67" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="H65" s="2" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
-      <c r="D66" s="2" t="s">
+      <c r="E67" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="E66" s="2" t="s">
+      <c r="F67" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="G67" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="F66" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
-      <c r="D67" s="2" t="s">
+      <c r="H67" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="15.95">
+      <c r="D68" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="E67" s="2" t="s">
+      <c r="E68" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="F67" s="2" t="s">
+      <c r="F68" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="G67" s="2" t="s">
+      <c r="G68" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="H67" s="2" t="s">
+      <c r="H68" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="68" spans="1:8" s="8" customFormat="1">
-      <c r="D68" s="2" t="s">
+    <row r="69" spans="1:8" ht="15.95">
+      <c r="D69" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="E68" s="8" t="s">
+      <c r="E69" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" s="8" customFormat="1" ht="15.95">
+      <c r="D70" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="E70" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="F68" s="8" t="s">
+      <c r="F70" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="G68" s="8" t="s">
+      <c r="G70" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="H68" s="8" t="s">
+      <c r="H70" s="8" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
-      <c r="A69" s="4"/>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
-    </row>
-    <row r="70" spans="1:8" ht="15.95">
-      <c r="D70" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" ht="15.95">
-      <c r="D71" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>402</v>
-      </c>
+    <row r="71" spans="1:8">
+      <c r="A71" s="4"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
     </row>
     <row r="72" spans="1:8" ht="15.95">
       <c r="D72" s="2" t="s">
         <v>403</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>403</v>
@@ -6128,13 +6199,13 @@
         <v>404</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>404</v>
@@ -6145,13 +6216,13 @@
         <v>405</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>121</v>
+        <v>55</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>121</v>
+        <v>55</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>123</v>
+        <v>57</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>405</v>
@@ -6162,13 +6233,13 @@
         <v>406</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>128</v>
+        <v>69</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>128</v>
+        <v>69</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>407</v>
+        <v>71</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>406</v>
@@ -6176,425 +6247,425 @@
     </row>
     <row r="76" spans="1:8" ht="15.95">
       <c r="D76" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>409</v>
+        <v>121</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>409</v>
+        <v>121</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>410</v>
+        <v>123</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="15.95">
       <c r="D77" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>61</v>
+        <v>128</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>61</v>
+        <v>128</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>63</v>
+        <v>409</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="15.95">
       <c r="D78" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="G78" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="E78" s="2" t="s">
+      <c r="H78" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="15.95">
+      <c r="D79" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E79" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F78" s="2" t="s">
+      <c r="F79" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G78" s="2" t="s">
+      <c r="G79" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H79" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="H78" s="2" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" ht="128.1">
-      <c r="A79" s="2" t="s">
+    </row>
+    <row r="80" spans="1:8" ht="15.95">
+      <c r="D80" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="D79" s="8" t="s">
+      <c r="E80" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G80" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="E79" s="8" t="s">
+      <c r="H80" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="128.1">
+      <c r="A81" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="F79" s="8" t="s">
+      <c r="D81" s="8" t="s">
         <v>417</v>
       </c>
-      <c r="G79" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="H79" s="8" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8">
-      <c r="A80" s="4"/>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
-    </row>
-    <row r="81" spans="1:8" ht="15.95">
-      <c r="A81" s="8"/>
-      <c r="B81" s="8"/>
-      <c r="C81" s="8"/>
-      <c r="D81" s="8" t="s">
+      <c r="E81" s="8" t="s">
         <v>418</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>419</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>419</v>
       </c>
       <c r="G81" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H81" s="8" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" s="4"/>
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+    </row>
+    <row r="83" spans="1:8" ht="15.95">
+      <c r="A83" s="8"/>
+      <c r="B83" s="8"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="8" t="s">
         <v>420</v>
       </c>
-      <c r="H81" s="8" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" s="9" customFormat="1" ht="48">
-      <c r="A82" s="8"/>
-      <c r="B82" s="8"/>
-      <c r="C82" s="8"/>
-      <c r="D82" s="8" t="s">
+      <c r="E83" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="E82" s="8" t="s">
+      <c r="F83" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="G83" s="8" t="s">
         <v>422</v>
       </c>
-      <c r="F82" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="G82" s="8" t="s">
+      <c r="H83" s="8" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" s="9" customFormat="1" ht="48">
+      <c r="A84" s="8"/>
+      <c r="B84" s="8"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="H82" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="15.95">
-      <c r="D83" s="2" t="s">
+      <c r="E84" s="8" t="s">
         <v>424</v>
       </c>
-      <c r="E83" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="G83" s="2" t="s">
+      <c r="F84" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="G84" s="8" t="s">
         <v>425</v>
       </c>
-      <c r="H83" s="2" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" ht="15.95">
-      <c r="D84" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>426</v>
+      <c r="H84" s="8" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="15.95">
       <c r="D85" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="G85" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="E85" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>429</v>
-      </c>
       <c r="H85" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="15.95">
       <c r="D86" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>431</v>
+        <v>299</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>431</v>
+        <v>299</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>432</v>
+        <v>300</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="15.95">
       <c r="D87" s="2" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="15.95">
       <c r="D88" s="2" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="15.95">
       <c r="D89" s="2" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="15.95">
       <c r="D90" s="2" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="15.95">
       <c r="D91" s="2" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="G91" s="8" t="s">
-        <v>447</v>
+        <v>442</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>443</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="15.95">
       <c r="D92" s="2" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="G92" s="8" t="s">
-        <v>450</v>
+        <v>445</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>446</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="15.95">
       <c r="D93" s="2" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="15.95">
       <c r="D94" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="G94" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="15.95">
+      <c r="D95" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E95" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="E94" s="2" t="s">
+      <c r="F95" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="G95" s="8" t="s">
         <v>455</v>
       </c>
-      <c r="F94" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="G94" s="8" t="s">
-        <v>456</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8">
-      <c r="A95" s="4"/>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
-      <c r="H95" s="4"/>
+      <c r="H95" s="2" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="96" spans="1:8" ht="15.95">
       <c r="D96" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E96" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="E96" s="2" t="s">
-        <v>434</v>
-      </c>
       <c r="F96" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>435</v>
+        <v>457</v>
+      </c>
+      <c r="G96" s="8" t="s">
+        <v>458</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" s="6" customFormat="1" ht="15.95">
-      <c r="A97" s="2"/>
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="G97" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>458</v>
-      </c>
+        <v>456</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" s="4"/>
+      <c r="B97" s="4"/>
+      <c r="C97" s="4"/>
+      <c r="D97" s="4"/>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4"/>
+      <c r="G97" s="4"/>
+      <c r="H97" s="4"/>
     </row>
     <row r="98" spans="1:8" ht="15.95">
       <c r="D98" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" s="6" customFormat="1" ht="15.95">
+      <c r="A99" s="2"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="E99" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="E98" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="G98" s="2" t="s">
+      <c r="F99" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="G99" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="H98" s="2" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" ht="15.95">
-      <c r="D99" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="G99" s="8" t="s">
-        <v>323</v>
-      </c>
       <c r="H99" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="15.95">
       <c r="D100" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="G100" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="E100" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="G100" s="8" t="s">
-        <v>331</v>
-      </c>
       <c r="H100" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="15.95">
@@ -6602,13 +6673,13 @@
         <v>465</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>301</v>
+        <v>325</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>465</v>
@@ -6619,13 +6690,13 @@
         <v>466</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>355</v>
+        <v>331</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>355</v>
+        <v>331</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>466</v>
@@ -6636,13 +6707,13 @@
         <v>467</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>468</v>
+        <v>302</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>468</v>
+        <v>302</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>469</v>
+        <v>303</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>467</v>
@@ -6650,53 +6721,53 @@
     </row>
     <row r="104" spans="1:8" ht="15.95">
       <c r="D104" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>471</v>
+        <v>357</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>471</v>
+        <v>357</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>472</v>
+        <v>358</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="105" spans="1:8" ht="15.95">
       <c r="D105" s="2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>343</v>
+        <v>470</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>343</v>
+        <v>470</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>307</v>
+        <v>471</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="15.95">
       <c r="D106" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="G106" s="8" t="s">
         <v>474</v>
       </c>
-      <c r="E106" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="F106" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="G106" s="8" t="s">
-        <v>307</v>
-      </c>
       <c r="H106" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="107" spans="1:8" ht="15.95">
@@ -6704,13 +6775,13 @@
         <v>475</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>306</v>
+        <v>345</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>306</v>
+        <v>345</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>475</v>
@@ -6721,180 +6792,187 @@
         <v>476</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15.95">
+    <row r="109" spans="1:8">
       <c r="D109" s="2" t="s">
         <v>477</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>343</v>
+        <v>478</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="G109" s="8" t="s">
-        <v>307</v>
+        <v>478</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>478</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="110" spans="1:8" ht="15.95">
       <c r="D110" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>349</v>
+        <v>308</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>349</v>
+        <v>308</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>350</v>
+        <v>309</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="15.95">
       <c r="D111" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E111" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="G111" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="H111" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="F111" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="G111" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="H111" s="2" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="15.95">
       <c r="D112" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="E112" s="2">
-        <v>1</v>
-      </c>
-      <c r="F112" s="2">
-        <v>1</v>
-      </c>
-      <c r="G112" s="2">
-        <v>1</v>
-      </c>
-      <c r="H112" s="2">
-        <v>1</v>
+        <v>481</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="G112" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="113" spans="1:8" ht="15.95">
       <c r="D113" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="G113" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" ht="15.95">
+      <c r="D114" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="E113" s="2" t="s">
+      <c r="E114" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="F113" s="2" t="s">
+      <c r="F114" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="G113" s="2" t="s">
+      <c r="G114" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="H113" s="2" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" ht="32.1">
-      <c r="D114" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="G114" s="2" t="s">
-        <v>487</v>
-      </c>
       <c r="H114" s="2" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="15.95">
       <c r="D115" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E115" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F115" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G115" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H115" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:8" ht="15.95">
       <c r="D116" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="G116" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="E116" s="2" t="s">
+      <c r="H116" s="2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="32.1">
+      <c r="D117" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="F116" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="G116" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="H116" s="2" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" ht="15.95">
-      <c r="D117" s="2" t="s">
+      <c r="E117" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="E117" s="2" t="s">
+      <c r="F117" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" ht="15.95">
+      <c r="D118" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="F117" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="G117" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="H117" s="2" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8">
-      <c r="A118" s="4"/>
-      <c r="B118" s="4"/>
-      <c r="C118" s="4"/>
-      <c r="D118" s="4"/>
-      <c r="E118" s="4"/>
-      <c r="F118" s="4"/>
-      <c r="G118" s="4"/>
-      <c r="H118" s="4"/>
+      <c r="E118" s="2">
+        <v>2</v>
+      </c>
+      <c r="F118" s="2">
+        <v>2</v>
+      </c>
+      <c r="G118" s="2">
+        <v>2</v>
+      </c>
+      <c r="H118" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="119" spans="1:8" ht="15.95">
       <c r="D119" s="2" t="s">
@@ -6907,887 +6985,898 @@
         <v>494</v>
       </c>
       <c r="G119" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" ht="15.95">
+      <c r="D120" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="H119" s="2" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" ht="48">
-      <c r="D120" s="2" t="s">
+      <c r="E120" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="E120" s="2" t="s">
-        <v>497</v>
-      </c>
       <c r="F120" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="15.95">
-      <c r="D121" s="2" t="s">
+    <row r="121" spans="1:8">
+      <c r="A121" s="4"/>
+      <c r="B121" s="4"/>
+      <c r="C121" s="4"/>
+      <c r="D121" s="4"/>
+      <c r="E121" s="4"/>
+      <c r="F121" s="4"/>
+      <c r="G121" s="4"/>
+      <c r="H121" s="4"/>
+    </row>
+    <row r="122" spans="1:8" ht="15.95">
+      <c r="D122" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="G122" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="E121" s="2" t="s">
+      <c r="H122" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" ht="48">
+      <c r="D123" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="F121" s="2" t="s">
+      <c r="E123" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="H123" s="2" t="s">
         <v>500</v>
-      </c>
-      <c r="G121" s="8" t="s">
-        <v>501</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8">
-      <c r="A122" s="4"/>
-      <c r="B122" s="4"/>
-      <c r="C122" s="4"/>
-      <c r="D122" s="4"/>
-      <c r="E122" s="4"/>
-      <c r="F122" s="4"/>
-      <c r="G122" s="4"/>
-      <c r="H122" s="4"/>
-    </row>
-    <row r="123" spans="1:8" ht="15.95">
-      <c r="D123" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="G123" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="15.95">
       <c r="D124" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="E124" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="E124" s="2" t="s">
+      <c r="F124" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="G124" s="8" t="s">
         <v>505</v>
       </c>
-      <c r="F124" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="G124" s="2" t="s">
-        <v>505</v>
-      </c>
       <c r="H124" s="2" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" ht="15.95">
-      <c r="D125" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="G125" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="H125" s="2" t="s">
-        <v>506</v>
-      </c>
+        <v>503</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" s="4"/>
+      <c r="B125" s="4"/>
+      <c r="C125" s="4"/>
+      <c r="D125" s="4"/>
+      <c r="E125" s="4"/>
+      <c r="F125" s="4"/>
+      <c r="G125" s="4"/>
+      <c r="H125" s="4"/>
     </row>
     <row r="126" spans="1:8" ht="15.95">
       <c r="D126" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="15.95">
       <c r="D127" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
     </row>
     <row r="128" spans="1:8" ht="15.95">
       <c r="D128" s="2" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
     </row>
     <row r="129" spans="1:8" ht="15.95">
       <c r="D129" s="2" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
     </row>
     <row r="130" spans="1:8" ht="15.95">
       <c r="D130" s="2" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="131" spans="1:8" ht="15.95">
       <c r="D131" s="2" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
     </row>
     <row r="132" spans="1:8" ht="15.95">
       <c r="D132" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" ht="15.95">
+      <c r="D133" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="G133" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="E132" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="F132" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="G132" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="H132" s="2" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8">
-      <c r="A133" s="4"/>
-      <c r="B133" s="4"/>
-      <c r="C133" s="4"/>
-      <c r="D133" s="4"/>
-      <c r="E133" s="4"/>
-      <c r="F133" s="4"/>
-      <c r="G133" s="4"/>
-      <c r="H133" s="4"/>
+      <c r="H133" s="2" t="s">
+        <v>525</v>
+      </c>
     </row>
     <row r="134" spans="1:8" ht="15.95">
       <c r="D134" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="G134" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="E134" s="2" t="s">
+      <c r="H134" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" ht="15.95">
+      <c r="D135" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="F134" s="8" t="s">
+      <c r="E135" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="H135" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="G134" s="8" t="s">
-        <v>532</v>
-      </c>
-      <c r="H134" s="2" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" ht="15.95">
-      <c r="D135" s="14" t="s">
-        <v>533</v>
-      </c>
-      <c r="E135" s="14" t="s">
-        <v>534</v>
-      </c>
-      <c r="F135" s="19" t="s">
-        <v>535</v>
-      </c>
-      <c r="G135" s="19" t="s">
-        <v>535</v>
-      </c>
-      <c r="H135" s="14" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" ht="15.95">
-      <c r="D136" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="E136" s="8" t="s">
-        <v>536</v>
-      </c>
-      <c r="F136" s="8" t="s">
-        <v>536</v>
-      </c>
-      <c r="G136" s="8" t="s">
-        <v>537</v>
-      </c>
-      <c r="H136" s="2" t="s">
-        <v>535</v>
-      </c>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" s="4"/>
+      <c r="B136" s="4"/>
+      <c r="C136" s="4"/>
+      <c r="D136" s="4"/>
+      <c r="E136" s="4"/>
+      <c r="F136" s="4"/>
+      <c r="G136" s="4"/>
+      <c r="H136" s="4"/>
     </row>
     <row r="137" spans="1:8" ht="15.95">
       <c r="D137" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="F137" s="8" t="s">
+        <v>535</v>
+      </c>
+      <c r="G137" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" ht="15.95">
+      <c r="D138" s="14" t="s">
+        <v>537</v>
+      </c>
+      <c r="E138" s="14" t="s">
         <v>538</v>
       </c>
-      <c r="E137" s="8" t="s">
+      <c r="F138" s="19" t="s">
         <v>539</v>
       </c>
-      <c r="F137" s="8" t="s">
+      <c r="G138" s="19" t="s">
         <v>539</v>
       </c>
-      <c r="G137" s="8" t="s">
-        <v>540</v>
-      </c>
-      <c r="H137" s="2" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" ht="32.1">
-      <c r="D138" s="14" t="s">
-        <v>541</v>
-      </c>
-      <c r="E138" s="14" t="s">
-        <v>542</v>
-      </c>
-      <c r="F138" s="19" t="s">
-        <v>535</v>
-      </c>
-      <c r="G138" s="19" t="s">
-        <v>535</v>
-      </c>
       <c r="H138" s="14" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
     </row>
     <row r="139" spans="1:8" ht="15.95">
       <c r="D139" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="E139" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="F139" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="G139" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" ht="15.95">
+      <c r="D140" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="E140" s="8" t="s">
         <v>543</v>
       </c>
-      <c r="E139" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="F139" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="G139" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="H139" s="2" t="s">
+      <c r="F140" s="8" t="s">
         <v>543</v>
       </c>
-    </row>
-    <row r="140" spans="1:8" ht="32.1">
-      <c r="D140" s="2" t="s">
+      <c r="G140" s="8" t="s">
         <v>544</v>
       </c>
-      <c r="E140" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F140" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="G140" s="8" t="s">
-        <v>310</v>
-      </c>
       <c r="H140" s="2" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" ht="15.95">
-      <c r="A141" s="4" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" ht="32.1">
+      <c r="D141" s="14" t="s">
         <v>545</v>
       </c>
-      <c r="B141" s="4"/>
-      <c r="C141" s="4"/>
-      <c r="D141" s="4"/>
-      <c r="E141" s="4"/>
-      <c r="F141" s="4"/>
-      <c r="G141" s="4"/>
-      <c r="H141" s="4"/>
+      <c r="E141" s="14" t="s">
+        <v>546</v>
+      </c>
+      <c r="F141" s="19" t="s">
+        <v>539</v>
+      </c>
+      <c r="G141" s="19" t="s">
+        <v>539</v>
+      </c>
+      <c r="H141" s="14" t="s">
+        <v>545</v>
+      </c>
     </row>
     <row r="142" spans="1:8" ht="15.95">
       <c r="D142" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="E142" s="2" t="s">
-        <v>539</v>
+        <v>547</v>
+      </c>
+      <c r="E142" s="8" t="s">
+        <v>308</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>539</v>
+        <v>308</v>
       </c>
       <c r="G142" s="8" t="s">
-        <v>540</v>
+        <v>309</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" ht="15.95">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" ht="32.1">
       <c r="D143" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="E143" s="2" t="s">
         <v>548</v>
       </c>
+      <c r="E143" s="8" t="s">
+        <v>311</v>
+      </c>
       <c r="F143" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H143" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="G143" s="8" t="s">
+    </row>
+    <row r="144" spans="1:8" ht="15.95">
+      <c r="A144" s="4" t="s">
         <v>549</v>
       </c>
-      <c r="H143" s="2" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" ht="15.95">
-      <c r="D144" s="2" t="s">
+      <c r="B144" s="4"/>
+      <c r="C144" s="4"/>
+      <c r="D144" s="4"/>
+      <c r="E144" s="4"/>
+      <c r="F144" s="4"/>
+      <c r="G144" s="4"/>
+      <c r="H144" s="4"/>
+    </row>
+    <row r="145" spans="1:8" ht="15.95">
+      <c r="D145" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="E144" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="F144" s="8" t="s">
-        <v>536</v>
-      </c>
-      <c r="G144" s="8" t="s">
-        <v>537</v>
-      </c>
-      <c r="H144" s="2" t="s">
+      <c r="E145" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="F145" s="8" t="s">
+        <v>543</v>
+      </c>
+      <c r="G145" s="8" t="s">
+        <v>544</v>
+      </c>
+      <c r="H145" s="2" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="145" spans="1:8">
-      <c r="A145" s="4"/>
-      <c r="B145" s="4"/>
-      <c r="C145" s="4"/>
-      <c r="D145" s="4"/>
-      <c r="E145" s="4"/>
-      <c r="F145" s="4"/>
-      <c r="G145" s="4"/>
-      <c r="H145" s="4"/>
-    </row>
-    <row r="146" spans="1:8" s="8" customFormat="1" ht="15.95">
-      <c r="D146" s="8" t="s">
+    <row r="146" spans="1:8" ht="15.95">
+      <c r="D146" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="E146" s="8" t="s">
+      <c r="E146" s="2" t="s">
         <v>552</v>
       </c>
       <c r="F146" s="8" t="s">
         <v>552</v>
       </c>
       <c r="G146" s="8" t="s">
-        <v>552</v>
-      </c>
-      <c r="H146" s="8" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" s="8" customFormat="1" ht="15.95">
-      <c r="D147" s="8" t="s">
         <v>553</v>
       </c>
-      <c r="E147" s="8" t="s">
+      <c r="H146" s="2" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" ht="15.95">
+      <c r="D147" s="2" t="s">
         <v>554</v>
       </c>
+      <c r="E147" s="2" t="s">
+        <v>540</v>
+      </c>
       <c r="F147" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="G147" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="H147" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="G147" s="8" t="s">
-        <v>554</v>
-      </c>
-      <c r="H147" s="8" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" s="8" customFormat="1" ht="15.95">
-      <c r="D148" s="8" t="s">
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" s="4"/>
+      <c r="B148" s="4"/>
+      <c r="C148" s="4"/>
+      <c r="D148" s="4"/>
+      <c r="E148" s="4"/>
+      <c r="F148" s="4"/>
+      <c r="G148" s="4"/>
+      <c r="H148" s="4"/>
+    </row>
+    <row r="149" spans="1:8" s="8" customFormat="1" ht="15.95">
+      <c r="D149" s="8" t="s">
         <v>555</v>
       </c>
-      <c r="E148" s="8" t="s">
+      <c r="E149" s="8" t="s">
         <v>556</v>
       </c>
-      <c r="F148" s="8" t="s">
+      <c r="F149" s="8" t="s">
         <v>556</v>
       </c>
-      <c r="G148" s="8" t="s">
+      <c r="G149" s="8" t="s">
         <v>556</v>
       </c>
-      <c r="H148" s="8" t="s">
+      <c r="H149" s="8" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="15.95">
-      <c r="A149" s="4" t="s">
+    <row r="150" spans="1:8" s="8" customFormat="1" ht="15.95">
+      <c r="D150" s="8" t="s">
         <v>557</v>
       </c>
-      <c r="B149" s="4"/>
-      <c r="C149" s="4"/>
-      <c r="D149" s="4"/>
-      <c r="E149" s="4"/>
-      <c r="F149" s="4"/>
-      <c r="G149" s="4"/>
-      <c r="H149" s="4"/>
-    </row>
-    <row r="150" spans="1:8" ht="15.95">
-      <c r="D150" s="2" t="s">
+      <c r="E150" s="8" t="s">
         <v>558</v>
       </c>
-      <c r="E150" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="F150" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="G150" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="H150" s="2" t="s">
+      <c r="F150" s="8" t="s">
+        <v>558</v>
+      </c>
+      <c r="G150" s="8" t="s">
+        <v>558</v>
+      </c>
+      <c r="H150" s="8" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" s="8" customFormat="1" ht="15.95">
+      <c r="D151" s="8" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="151" spans="1:8" ht="15.95">
-      <c r="D151" s="11" t="s">
+      <c r="E151" s="8" t="s">
         <v>560</v>
       </c>
-      <c r="E151" s="11" t="s">
+      <c r="F151" s="8" t="s">
+        <v>560</v>
+      </c>
+      <c r="G151" s="8" t="s">
+        <v>560</v>
+      </c>
+      <c r="H151" s="8" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" ht="15.95">
+      <c r="A152" s="4" t="s">
         <v>561</v>
       </c>
-      <c r="F151" s="11" t="s">
-        <v>561</v>
-      </c>
-      <c r="G151" s="11" t="s">
+      <c r="B152" s="4"/>
+      <c r="C152" s="4"/>
+      <c r="D152" s="4"/>
+      <c r="E152" s="4"/>
+      <c r="F152" s="4"/>
+      <c r="G152" s="4"/>
+      <c r="H152" s="4"/>
+    </row>
+    <row r="153" spans="1:8" ht="15.95">
+      <c r="D153" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="H151" s="11" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" ht="15.95">
-      <c r="D152" s="11" t="s">
-        <v>563</v>
-      </c>
-      <c r="E152" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="F152" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="G152" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="H152" s="11" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" ht="15.95">
-      <c r="D153" s="11" t="s">
-        <v>564</v>
-      </c>
-      <c r="E153" s="11" t="s">
-        <v>565</v>
-      </c>
-      <c r="F153" s="11" t="s">
-        <v>565</v>
-      </c>
-      <c r="G153" s="11" t="s">
-        <v>566</v>
-      </c>
-      <c r="H153" s="11" t="s">
-        <v>559</v>
+      <c r="E153" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="154" spans="1:8" ht="15.95">
       <c r="D154" s="11" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="E154" s="11" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="F154" s="11" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="G154" s="11" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="H154" s="11" t="s">
-        <v>559</v>
+        <v>478</v>
       </c>
     </row>
     <row r="155" spans="1:8" ht="15.95">
       <c r="D155" s="11" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="E155" s="11" t="s">
-        <v>569</v>
+        <v>478</v>
       </c>
       <c r="F155" s="11" t="s">
-        <v>569</v>
+        <v>478</v>
       </c>
       <c r="G155" s="11" t="s">
-        <v>570</v>
+        <v>478</v>
       </c>
       <c r="H155" s="11" t="s">
-        <v>559</v>
+        <v>478</v>
       </c>
     </row>
     <row r="156" spans="1:8" ht="15.95">
       <c r="D156" s="11" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="E156" s="11" t="s">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="F156" s="11" t="s">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="G156" s="11" t="s">
-        <v>559</v>
+        <v>569</v>
       </c>
       <c r="H156" s="11" t="s">
-        <v>559</v>
+        <v>478</v>
       </c>
     </row>
     <row r="157" spans="1:8" ht="15.95">
       <c r="D157" s="11" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E157" s="11" t="s">
-        <v>573</v>
+        <v>478</v>
       </c>
       <c r="F157" s="11" t="s">
-        <v>573</v>
+        <v>478</v>
       </c>
       <c r="G157" s="11" t="s">
-        <v>574</v>
+        <v>478</v>
       </c>
       <c r="H157" s="11" t="s">
-        <v>559</v>
+        <v>478</v>
       </c>
     </row>
     <row r="158" spans="1:8" ht="15.95">
       <c r="D158" s="11" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="E158" s="11" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="F158" s="11" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="G158" s="11" t="s">
-        <v>559</v>
+        <v>573</v>
       </c>
       <c r="H158" s="11" t="s">
-        <v>559</v>
+        <v>478</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="15.95">
       <c r="D159" s="11" t="s">
+        <v>574</v>
+      </c>
+      <c r="E159" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="F159" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="G159" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="H159" s="11" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" ht="15.95">
+      <c r="D160" s="11" t="s">
+        <v>575</v>
+      </c>
+      <c r="E160" s="11" t="s">
         <v>576</v>
       </c>
-      <c r="E159" s="11" t="s">
+      <c r="F160" s="11" t="s">
+        <v>576</v>
+      </c>
+      <c r="G160" s="11" t="s">
         <v>577</v>
       </c>
-      <c r="F159" s="11" t="s">
-        <v>577</v>
-      </c>
-      <c r="G159" s="11" t="s">
-        <v>578</v>
-      </c>
-      <c r="H159" s="11" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" ht="48">
-      <c r="D160" s="11" t="s">
-        <v>579</v>
-      </c>
-      <c r="E160" s="11" t="s">
-        <v>580</v>
-      </c>
-      <c r="F160" s="11" t="s">
-        <v>581</v>
-      </c>
-      <c r="G160" s="11" t="s">
-        <v>582</v>
-      </c>
       <c r="H160" s="11" t="s">
-        <v>559</v>
+        <v>478</v>
       </c>
     </row>
     <row r="161" spans="4:8" ht="15.95">
       <c r="D161" s="11" t="s">
+        <v>578</v>
+      </c>
+      <c r="E161" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="F161" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="G161" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="H161" s="11" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="162" spans="4:8" ht="15.95">
+      <c r="D162" s="11" t="s">
+        <v>579</v>
+      </c>
+      <c r="E162" s="11" t="s">
+        <v>580</v>
+      </c>
+      <c r="F162" s="11" t="s">
+        <v>580</v>
+      </c>
+      <c r="G162" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="H162" s="11" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="163" spans="4:8" ht="48">
+      <c r="D163" s="11" t="s">
+        <v>582</v>
+      </c>
+      <c r="E163" s="11" t="s">
         <v>583</v>
       </c>
-      <c r="E161" s="11" t="s">
+      <c r="F163" s="11" t="s">
         <v>584</v>
       </c>
-      <c r="F161" s="11" t="s">
-        <v>584</v>
-      </c>
-      <c r="G161" s="11" t="s">
+      <c r="G163" s="11" t="s">
         <v>585</v>
       </c>
-      <c r="H161" s="11" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="162" spans="4:8" ht="32.1">
-      <c r="D162" s="11" t="s">
-        <v>586</v>
-      </c>
-      <c r="E162" s="11" t="s">
-        <v>587</v>
-      </c>
-      <c r="F162" s="11" t="s">
-        <v>587</v>
-      </c>
-      <c r="G162" s="11" t="s">
-        <v>588</v>
-      </c>
-      <c r="H162" s="11" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="163" spans="4:8" ht="15.95">
-      <c r="D163" s="11" t="s">
-        <v>589</v>
-      </c>
-      <c r="E163" s="11" t="s">
-        <v>590</v>
-      </c>
-      <c r="F163" s="11" t="s">
-        <v>590</v>
-      </c>
-      <c r="G163" s="11" t="s">
-        <v>591</v>
-      </c>
       <c r="H163" s="11" t="s">
-        <v>559</v>
+        <v>478</v>
       </c>
     </row>
     <row r="164" spans="4:8" ht="15.95">
       <c r="D164" s="11" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="E164" s="11" t="s">
-        <v>559</v>
+        <v>587</v>
       </c>
       <c r="F164" s="11" t="s">
-        <v>559</v>
+        <v>587</v>
       </c>
       <c r="G164" s="11" t="s">
-        <v>559</v>
+        <v>588</v>
       </c>
       <c r="H164" s="11" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="165" spans="4:8" ht="15.95">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="165" spans="4:8" ht="32.1">
       <c r="D165" s="11" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="E165" s="11" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="F165" s="11" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="G165" s="11" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="H165" s="11" t="s">
-        <v>559</v>
+        <v>478</v>
       </c>
     </row>
     <row r="166" spans="4:8" ht="15.95">
       <c r="D166" s="11" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="E166" s="11" t="s">
-        <v>559</v>
+        <v>593</v>
       </c>
       <c r="F166" s="11" t="s">
-        <v>559</v>
+        <v>593</v>
       </c>
       <c r="G166" s="11" t="s">
-        <v>559</v>
+        <v>594</v>
       </c>
       <c r="H166" s="11" t="s">
-        <v>559</v>
+        <v>478</v>
       </c>
     </row>
     <row r="167" spans="4:8" ht="15.95">
       <c r="D167" s="11" t="s">
+        <v>595</v>
+      </c>
+      <c r="E167" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="F167" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="G167" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="H167" s="11" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="168" spans="4:8" ht="15.95">
+      <c r="D168" s="11" t="s">
+        <v>596</v>
+      </c>
+      <c r="E168" s="11" t="s">
         <v>597</v>
       </c>
-      <c r="E167" s="11" t="s">
+      <c r="F168" s="11" t="s">
+        <v>597</v>
+      </c>
+      <c r="G168" s="11" t="s">
         <v>598</v>
       </c>
-      <c r="F167" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="G167" s="11" t="s">
-        <v>598</v>
-      </c>
-      <c r="H167" s="11" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="168" spans="4:8" ht="48">
-      <c r="D168" s="11" t="s">
-        <v>599</v>
-      </c>
-      <c r="E168" s="11" t="s">
-        <v>600</v>
-      </c>
-      <c r="F168" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="G168" s="11" t="s">
-        <v>600</v>
-      </c>
       <c r="H168" s="11" t="s">
-        <v>559</v>
+        <v>478</v>
       </c>
     </row>
     <row r="169" spans="4:8" ht="15.95">
       <c r="D169" s="11" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E169" s="11" t="s">
-        <v>602</v>
+        <v>478</v>
       </c>
       <c r="F169" s="11" t="s">
-        <v>602</v>
+        <v>478</v>
       </c>
       <c r="G169" s="11" t="s">
-        <v>602</v>
+        <v>478</v>
       </c>
       <c r="H169" s="11" t="s">
-        <v>602</v>
+        <v>478</v>
       </c>
     </row>
     <row r="170" spans="4:8" ht="15.95">
       <c r="D170" s="11" t="s">
+        <v>600</v>
+      </c>
+      <c r="E170" s="11" t="s">
+        <v>601</v>
+      </c>
+      <c r="F170" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="G170" s="11" t="s">
+        <v>601</v>
+      </c>
+      <c r="H170" s="11" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="171" spans="4:8" ht="48">
+      <c r="D171" s="11" t="s">
+        <v>602</v>
+      </c>
+      <c r="E171" s="11" t="s">
         <v>603</v>
       </c>
-      <c r="E170" s="11" t="s">
+      <c r="F171" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="G171" s="11" t="s">
+        <v>603</v>
+      </c>
+      <c r="H171" s="11" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="172" spans="4:8" ht="15.95">
+      <c r="D172" s="11" t="s">
         <v>604</v>
       </c>
-      <c r="F170" s="11" t="s">
-        <v>604</v>
-      </c>
-      <c r="G170" s="11" t="s">
-        <v>604</v>
-      </c>
-      <c r="H170" s="11" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="171" spans="4:8" ht="15.95">
-      <c r="D171" s="14" t="s">
+      <c r="E172" s="11" t="s">
         <v>605</v>
       </c>
-      <c r="E171" s="14" t="s">
+      <c r="F172" s="11" t="s">
+        <v>605</v>
+      </c>
+      <c r="G172" s="11" t="s">
+        <v>605</v>
+      </c>
+      <c r="H172" s="11" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="173" spans="4:8" ht="15.95">
+      <c r="D173" s="11" t="s">
         <v>606</v>
       </c>
-      <c r="F171" s="14"/>
-      <c r="G171" s="14"/>
-      <c r="H171" s="14"/>
-    </row>
-    <row r="172" spans="4:8" ht="15.95">
-      <c r="D172" s="14" t="s">
+      <c r="E173" s="11" t="s">
         <v>607</v>
       </c>
-      <c r="E172" s="14" t="s">
-        <v>565</v>
-      </c>
-      <c r="F172" s="14"/>
-      <c r="G172" s="14"/>
-      <c r="H172" s="14"/>
-    </row>
-    <row r="173" spans="4:8" ht="32.1">
-      <c r="D173" s="14" t="s">
-        <v>608</v>
-      </c>
-      <c r="E173" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="F173" s="14"/>
-      <c r="G173" s="14"/>
-      <c r="H173" s="14"/>
+      <c r="F173" s="11" t="s">
+        <v>607</v>
+      </c>
+      <c r="G173" s="11" t="s">
+        <v>607</v>
+      </c>
+      <c r="H173" s="11" t="s">
+        <v>607</v>
+      </c>
     </row>
     <row r="174" spans="4:8" ht="15.95">
       <c r="D174" s="14" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="E174" s="14" t="s">
-        <v>573</v>
+        <v>609</v>
       </c>
       <c r="F174" s="14"/>
       <c r="G174" s="14"/>
@@ -7795,10 +7884,10 @@
     </row>
     <row r="175" spans="4:8" ht="15.95">
       <c r="D175" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="E175" s="14" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="F175" s="14"/>
       <c r="G175" s="14"/>
@@ -7806,7 +7895,7 @@
     </row>
     <row r="176" spans="4:8" ht="32.1">
       <c r="D176" s="14" t="s">
-        <v>575</v>
+        <v>611</v>
       </c>
       <c r="E176" s="14" t="s">
         <v>612</v>
@@ -7820,7 +7909,7 @@
         <v>613</v>
       </c>
       <c r="E177" s="14" t="s">
-        <v>614</v>
+        <v>576</v>
       </c>
       <c r="F177" s="14"/>
       <c r="G177" s="14"/>
@@ -7828,32 +7917,32 @@
     </row>
     <row r="178" spans="4:8" ht="15.95">
       <c r="D178" s="14" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E178" s="14" t="s">
-        <v>616</v>
+        <v>576</v>
       </c>
       <c r="F178" s="14"/>
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
     </row>
-    <row r="179" spans="4:8" ht="15.95">
+    <row r="179" spans="4:8" ht="32.1">
       <c r="D179" s="14" t="s">
-        <v>617</v>
+        <v>578</v>
       </c>
       <c r="E179" s="14" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="F179" s="14"/>
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
     </row>
-    <row r="180" spans="4:8" ht="32.1">
+    <row r="180" spans="4:8" ht="15.95">
       <c r="D180" s="14" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="E180" s="14" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="F180" s="14"/>
       <c r="G180" s="14"/>
@@ -7861,10 +7950,10 @@
     </row>
     <row r="181" spans="4:8" ht="15.95">
       <c r="D181" s="14" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="E181" s="14" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="F181" s="14"/>
       <c r="G181" s="14"/>
@@ -7872,21 +7961,21 @@
     </row>
     <row r="182" spans="4:8" ht="15.95">
       <c r="D182" s="14" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="E182" s="14" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="F182" s="14"/>
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
     </row>
-    <row r="183" spans="4:8" ht="48">
+    <row r="183" spans="4:8" ht="32.1">
       <c r="D183" s="14" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="E183" s="14" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="F183" s="14"/>
       <c r="G183" s="14"/>
@@ -7894,10 +7983,10 @@
     </row>
     <row r="184" spans="4:8" ht="15.95">
       <c r="D184" s="14" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="E184" s="14" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="F184" s="14"/>
       <c r="G184" s="14"/>
@@ -7905,32 +7994,32 @@
     </row>
     <row r="185" spans="4:8" ht="15.95">
       <c r="D185" s="14" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="E185" s="14" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="F185" s="14"/>
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
     </row>
-    <row r="186" spans="4:8" ht="15.95">
+    <row r="186" spans="4:8" ht="48">
       <c r="D186" s="14" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="E186" s="14" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="F186" s="14"/>
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
     </row>
-    <row r="187" spans="4:8" ht="32.1">
+    <row r="187" spans="4:8" ht="15.95">
       <c r="D187" s="14" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="E187" s="14" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="F187" s="14"/>
       <c r="G187" s="14"/>
@@ -7938,10 +8027,10 @@
     </row>
     <row r="188" spans="4:8" ht="15.95">
       <c r="D188" s="14" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="E188" s="14" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="F188" s="14"/>
       <c r="G188" s="14"/>
@@ -7949,21 +8038,21 @@
     </row>
     <row r="189" spans="4:8" ht="15.95">
       <c r="D189" s="14" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="E189" s="14" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="F189" s="14"/>
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
     </row>
-    <row r="190" spans="4:8" ht="15.95">
+    <row r="190" spans="4:8" ht="32.1">
       <c r="D190" s="14" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="E190" s="14" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -7971,10 +8060,10 @@
     </row>
     <row r="191" spans="4:8" ht="15.95">
       <c r="D191" s="14" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="E191" s="14" t="s">
-        <v>628</v>
+        <v>639</v>
       </c>
       <c r="F191" s="14"/>
       <c r="G191" s="14"/>
@@ -7982,370 +8071,314 @@
     </row>
     <row r="192" spans="4:8" ht="15.95">
       <c r="D192" s="14" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E192" s="14" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="F192" s="14"/>
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
     </row>
-    <row r="193" spans="1:8" ht="15.95">
+    <row r="193" spans="4:8" ht="15.95">
       <c r="D193" s="14" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E193" s="14" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="F193" s="14"/>
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
     </row>
-    <row r="194" spans="1:8" ht="48">
+    <row r="194" spans="4:8" ht="15.95">
       <c r="D194" s="14" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E194" s="14" t="s">
-        <v>647</v>
+        <v>631</v>
       </c>
       <c r="F194" s="14"/>
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
     </row>
-    <row r="195" spans="1:8" ht="15.95">
+    <row r="195" spans="4:8" ht="15.95">
       <c r="D195" s="14" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="E195" s="14" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="F195" s="14"/>
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
     </row>
-    <row r="196" spans="1:8" ht="15.95">
+    <row r="196" spans="4:8" ht="15.95">
       <c r="D196" s="14" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="E196" s="14" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="F196" s="14"/>
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
     </row>
-    <row r="197" spans="1:8" ht="15.95">
-      <c r="A197" s="4" t="s">
+    <row r="197" spans="4:8" ht="48">
+      <c r="D197" s="14" t="s">
+        <v>649</v>
+      </c>
+      <c r="E197" s="14" t="s">
+        <v>650</v>
+      </c>
+      <c r="F197" s="14"/>
+      <c r="G197" s="14"/>
+      <c r="H197" s="14"/>
+    </row>
+    <row r="198" spans="4:8" ht="15.95">
+      <c r="D198" s="14" t="s">
+        <v>651</v>
+      </c>
+      <c r="E198" s="14" t="s">
         <v>652</v>
       </c>
-      <c r="B197" s="4"/>
-      <c r="C197" s="4"/>
-      <c r="D197" s="4"/>
-      <c r="E197" s="4"/>
-      <c r="F197" s="4"/>
-      <c r="G197" s="4"/>
-      <c r="H197" s="4"/>
-    </row>
-    <row r="198" spans="1:8" ht="15.95">
-      <c r="D198" s="2" t="s">
+      <c r="F198" s="14"/>
+      <c r="G198" s="14"/>
+      <c r="H198" s="14"/>
+    </row>
+    <row r="199" spans="4:8" ht="15.95">
+      <c r="D199" s="14" t="s">
         <v>653</v>
       </c>
-      <c r="E198" s="2" t="s">
+      <c r="E199" s="14" t="s">
         <v>654</v>
       </c>
-      <c r="F198" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="G198" s="2" t="s">
+      <c r="F199" s="14"/>
+      <c r="G199" s="14"/>
+      <c r="H199" s="14"/>
+    </row>
+    <row r="200" spans="4:8" ht="15.95">
+      <c r="D200" s="14" t="s">
         <v>655</v>
       </c>
-      <c r="H198" s="2" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="199" spans="1:8" ht="15.95">
-      <c r="D199" s="2" t="s">
+      <c r="E200" s="14" t="s">
+        <v>639</v>
+      </c>
+      <c r="F200" s="14"/>
+      <c r="G200" s="14"/>
+      <c r="H200" s="14"/>
+    </row>
+    <row r="201" spans="4:8" ht="32.1">
+      <c r="D201" s="14" t="s">
         <v>656</v>
       </c>
-      <c r="E199" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="F199" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="G199" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="H199" s="2" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="200" spans="1:8" ht="15.95">
-      <c r="D200" s="2" t="s">
+      <c r="E201" s="14" t="s">
         <v>657</v>
       </c>
-      <c r="E200" s="2" t="s">
+      <c r="F201" s="14"/>
+      <c r="G201" s="14"/>
+      <c r="H201" s="14"/>
+    </row>
+    <row r="202" spans="4:8" ht="15.95">
+      <c r="D202" s="14" t="s">
         <v>658</v>
       </c>
-      <c r="F200" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="G200" s="2" t="s">
+      <c r="E202" s="14" t="s">
+        <v>560</v>
+      </c>
+      <c r="F202" s="14"/>
+      <c r="G202" s="14"/>
+      <c r="H202" s="14"/>
+    </row>
+    <row r="203" spans="4:8" ht="15.95">
+      <c r="D203" s="14" t="s">
         <v>659</v>
       </c>
-      <c r="H200" s="2" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="201" spans="1:8" ht="15.95">
-      <c r="D201" s="2" t="s">
+      <c r="E203" s="14" t="s">
         <v>660</v>
       </c>
-      <c r="E201" s="2" t="s">
+      <c r="F203" s="14"/>
+      <c r="G203" s="14"/>
+      <c r="H203" s="14"/>
+    </row>
+    <row r="204" spans="4:8" ht="15.95">
+      <c r="D204" s="14" t="s">
         <v>661</v>
       </c>
-      <c r="F201" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="G201" s="2" t="s">
+      <c r="E204" s="14" t="s">
         <v>662</v>
       </c>
-      <c r="H201" s="2" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="202" spans="1:8" ht="20.25" customHeight="1">
-      <c r="D202" s="2" t="s">
+      <c r="F204" s="14"/>
+      <c r="G204" s="14"/>
+      <c r="H204" s="14"/>
+    </row>
+    <row r="205" spans="4:8" ht="80.099999999999994">
+      <c r="D205" s="14" t="s">
         <v>663</v>
       </c>
-      <c r="E202" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="F202" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="G202" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="H202" s="2" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="203" spans="1:8" ht="15.95">
-      <c r="D203" s="2" t="s">
+      <c r="E205" s="14" t="s">
         <v>664</v>
       </c>
-      <c r="E203" s="2" t="s">
+      <c r="F205" s="14"/>
+      <c r="G205" s="14"/>
+      <c r="H205" s="14"/>
+    </row>
+    <row r="206" spans="4:8" ht="15.95">
+      <c r="D206" s="14" t="s">
         <v>665</v>
       </c>
-      <c r="F203" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="G203" s="2" t="s">
+      <c r="E206" s="14" t="s">
         <v>666</v>
       </c>
-      <c r="H203" s="2" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="204" spans="1:8" ht="32.1">
-      <c r="A204" s="4" t="s">
+      <c r="F206" s="14"/>
+      <c r="G206" s="14"/>
+      <c r="H206" s="14"/>
+    </row>
+    <row r="207" spans="4:8" ht="15.95">
+      <c r="D207" s="14" t="s">
         <v>667</v>
       </c>
-      <c r="B204" s="4"/>
-      <c r="C204" s="4"/>
-      <c r="D204" s="4"/>
-      <c r="E204" s="4"/>
-      <c r="F204" s="4"/>
-      <c r="G204" s="4"/>
-      <c r="H204" s="4"/>
-    </row>
-    <row r="205" spans="1:8" ht="15.95">
-      <c r="D205" s="2" t="s">
+      <c r="E207" s="14" t="s">
         <v>668</v>
       </c>
-      <c r="E205" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="F205" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="G205" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="H205" s="2" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="206" spans="1:8" ht="15.95">
-      <c r="D206" s="2" t="s">
+      <c r="F207" s="14"/>
+      <c r="G207" s="14"/>
+      <c r="H207" s="14"/>
+    </row>
+    <row r="208" spans="4:8" ht="15.95">
+      <c r="D208" s="14" t="s">
         <v>669</v>
       </c>
-      <c r="E206" s="2" t="s">
+      <c r="E208" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="F206" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="G206" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="H206" s="2" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="207" spans="1:8" ht="15.95">
-      <c r="D207" s="2" t="s">
+      <c r="F208" s="14"/>
+      <c r="G208" s="14"/>
+      <c r="H208" s="14"/>
+    </row>
+    <row r="209" spans="1:8" ht="48">
+      <c r="D209" s="14" t="s">
         <v>671</v>
       </c>
-      <c r="E207" s="2" t="s">
+      <c r="E209" s="14" t="s">
         <v>672</v>
       </c>
-      <c r="F207" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="G207" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="H207" s="2" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="208" spans="1:8" ht="15.95">
-      <c r="D208" s="2" t="s">
+      <c r="F209" s="14"/>
+      <c r="G209" s="14"/>
+      <c r="H209" s="14"/>
+    </row>
+    <row r="210" spans="1:8" ht="15.95">
+      <c r="A210" s="4" t="s">
         <v>673</v>
       </c>
-      <c r="E208" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="F208" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="G208" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="H208" s="2" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="209" spans="1:8" ht="15.95">
-      <c r="D209" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="E209" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="F209" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="G209" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="H209" s="2" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="210" spans="1:8" ht="15.95">
-      <c r="D210" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="E210" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="F210" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="G210" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="H210" s="2" t="s">
-        <v>559</v>
-      </c>
+      <c r="B210" s="4"/>
+      <c r="C210" s="4"/>
+      <c r="D210" s="4"/>
+      <c r="E210" s="4"/>
+      <c r="F210" s="4"/>
+      <c r="G210" s="4"/>
+      <c r="H210" s="4"/>
     </row>
     <row r="211" spans="1:8" ht="15.95">
       <c r="D211" s="2" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>559</v>
+        <v>676</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>559</v>
+        <v>478</v>
       </c>
     </row>
     <row r="212" spans="1:8" ht="15.95">
       <c r="D212" s="2" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>682</v>
+        <v>478</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>682</v>
+        <v>478</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>559</v>
+        <v>478</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>559</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:8" ht="15.95">
       <c r="D213" s="2" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>559</v>
+        <v>680</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>559</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:8" ht="15.95">
       <c r="D214" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="F214" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="G214" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="H214" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" ht="20.25" customHeight="1">
+      <c r="D215" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="F215" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="G215" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H215" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" ht="15.95">
+      <c r="D216" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="E214" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="F214" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="G214" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="H214" s="2" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="215" spans="1:8" ht="15.95">
-      <c r="D215" s="2" t="s">
+      <c r="E216" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="E215" s="2" t="s">
+      <c r="F216" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="G216" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="F215" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="G215" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="H215" s="2" t="s">
-        <v>559</v>
+      <c r="H216" s="2" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="217" spans="1:8" ht="32.1">
@@ -8365,156 +8398,389 @@
         <v>689</v>
       </c>
       <c r="E218" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="F218" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="G218" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H218" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" ht="15.95">
+      <c r="D219" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="F218" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="G218" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="H218" s="2" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="219" spans="1:8" ht="32.1">
-      <c r="D219" s="2" t="s">
+      <c r="E219" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E219" s="2" t="s">
+      <c r="F219" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="G219" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H219" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" ht="15.95">
+      <c r="D220" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="F219" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="G219" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="H219" s="2" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="220" spans="1:8" ht="32.1">
-      <c r="D220" s="2" t="s">
+      <c r="E220" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="E220" s="2" t="s">
+      <c r="F220" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="G220" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H220" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" ht="15.95">
+      <c r="D221" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="F220" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="G220" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="H220" s="2" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="221" spans="1:8" ht="32.1">
-      <c r="D221" s="2" t="s">
+      <c r="E221" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="E221" s="2" t="s">
-        <v>696</v>
-      </c>
       <c r="F221" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>559</v>
+        <v>478</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>559</v>
+        <v>478</v>
       </c>
     </row>
     <row r="222" spans="1:8" ht="15.95">
       <c r="D222" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="E222" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="E222" s="2" t="s">
-        <v>698</v>
-      </c>
       <c r="F222" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>559</v>
+        <v>478</v>
       </c>
       <c r="H222" s="2" t="s">
-        <v>559</v>
+        <v>478</v>
       </c>
     </row>
     <row r="223" spans="1:8" ht="15.95">
       <c r="D223" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="E223" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="E223" s="2" t="s">
+      <c r="F223" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="G223" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H223" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" ht="15.95">
+      <c r="D224" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="F223" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="G223" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="H223" s="2" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="224" spans="1:8" ht="32.1">
-      <c r="D224" s="2" t="s">
+      <c r="E224" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="E224" s="2" t="s">
+      <c r="F224" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="G224" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H224" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8 16384:16384" ht="15.95">
+      <c r="D225" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="F224" s="2" t="s">
-        <v>702</v>
-      </c>
-      <c r="G224" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="H224" s="2" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="225" spans="4:8 16384:16384" ht="32.1">
-      <c r="D225" s="2" t="s">
+      <c r="E225" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="E225" s="2" t="s">
-        <v>559</v>
-      </c>
       <c r="F225" s="2" t="s">
-        <v>559</v>
+        <v>703</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>559</v>
+        <v>478</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="226" spans="4:8 16384:16384" ht="48">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8 16384:16384" ht="15.95">
       <c r="D226" s="2" t="s">
         <v>704</v>
       </c>
       <c r="E226" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="F226" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="G226" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H226" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8 16384:16384" ht="15.95">
+      <c r="D227" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="E227" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F227" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G227" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H227" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8 16384:16384" ht="15.95">
+      <c r="D228" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="F228" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="G228" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H228" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8 16384:16384" ht="32.1">
+      <c r="A230" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="B230" s="4"/>
+      <c r="C230" s="4"/>
+      <c r="D230" s="4"/>
+      <c r="E230" s="4"/>
+      <c r="F230" s="4"/>
+      <c r="G230" s="4"/>
+      <c r="H230" s="4"/>
+    </row>
+    <row r="231" spans="1:8 16384:16384" ht="15.95">
+      <c r="D231" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="F231" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="G231" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H231" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8 16384:16384" ht="32.1">
+      <c r="D232" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="F232" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="G232" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H232" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8 16384:16384" ht="32.1">
+      <c r="D233" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="F233" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="G233" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H233" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8 16384:16384" ht="32.1">
+      <c r="D234" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="F234" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="G234" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H234" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8 16384:16384" ht="15.95">
+      <c r="D235" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="E235" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="F235" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="G235" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H235" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8 16384:16384" ht="15.95">
+      <c r="D236" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="F236" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="G236" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H236" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8 16384:16384" ht="32.1">
+      <c r="D237" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="F237" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="G237" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H237" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8 16384:16384" ht="32.1">
+      <c r="D238" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="F238" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="G238" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H238" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8 16384:16384" ht="48">
+      <c r="D239" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="E239" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="F226" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="G226" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="H226" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="XFD226" s="2" t="s">
-        <v>559</v>
-      </c>
+      <c r="F239" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="G239" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H239" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="XFD239" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8 16384:16384" ht="15.95">
+      <c r="A240" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="B240" s="4"/>
+      <c r="C240" s="4"/>
+      <c r="D240" s="4"/>
+      <c r="E240" s="4"/>
+      <c r="F240" s="4"/>
+      <c r="G240" s="4"/>
+      <c r="H240" s="4"/>
+    </row>
+    <row r="241" spans="4:8" ht="15.95">
+      <c r="D241" s="14" t="s">
+        <v>727</v>
+      </c>
+      <c r="E241" s="14" t="s">
+        <v>728</v>
+      </c>
+      <c r="F241" s="14"/>
+      <c r="G241" s="14"/>
+      <c r="H241" s="14"/>
+    </row>
+    <row r="242" spans="4:8" ht="48">
+      <c r="D242" s="14" t="s">
+        <v>729</v>
+      </c>
+      <c r="E242" s="14" t="s">
+        <v>730</v>
+      </c>
+      <c r="F242" s="14"/>
+      <c r="G242" s="14"/>
+      <c r="H242" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8526,6 +8792,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -8534,7 +8806,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001735E4C1AF81B044B42502EF65468AD3" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b06dd55da7e75ffac548536a232936d2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eadb902b-93b7-47a6-8130-18fdf8801a21" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="033944ded8f040f3b5ba86892713db09" ns2:_="">
     <xsd:import namespace="eadb902b-93b7-47a6-8130-18fdf8801a21"/>
@@ -8666,20 +8938,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE5E5259-1F31-433F-8613-391F4D2D66AE}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FBDCD96-85A7-4ED3-BEE8-F34479CB9646}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B7D05CE-367F-41E4-8608-7D898D6C11DA}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE5E5259-1F31-433F-8613-391F4D2D66AE}"/>
 </file>